--- a/files/MostProdCountries.xlsx
+++ b/files/MostProdCountries.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -35,522 +35,516 @@
     <t xml:space="preserve">USA            </t>
   </si>
   <si>
-    <t xml:space="preserve">2104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0490</t>
+    <t xml:space="preserve">2089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANADA         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.038945</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 109</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1615</t>
   </si>
   <si>
     <t xml:space="preserve">CHINA          </t>
   </si>
   <si>
-    <t xml:space="preserve"> 144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.041848</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 119</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANADA         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.038070</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 111</t>
+    <t xml:space="preserve"> 123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  96</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSTRALIA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.033553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  82</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNITED KINGDOM </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.031456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  76</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITALY          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.023667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  44</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURKEY         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.020371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPAIN          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  39</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3810</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAPAN          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NETHERLANDS    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  41</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWEDEN         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW ZEALAND    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  13</t>
   </si>
   <si>
     <t xml:space="preserve"> 20</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUSTRALIA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.033130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  84</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNITED KINGDOM </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.032549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  81</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITALY          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.023830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  46</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPAIN          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.019471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TURKEY         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  63</t>
+    <t xml:space="preserve">0.6061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERMANY        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  25</t>
   </si>
   <si>
     <t xml:space="preserve">  4</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAPAN          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.016856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  8</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.1379</t>
   </si>
   <si>
-    <t xml:space="preserve">NETHERLANDS    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.015402</t>
+    <t xml:space="preserve">BRAZIL         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOREA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRELAND        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELGIUM        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRAN           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORWAY         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   9</t>
   </si>
   <si>
     <t xml:space="preserve"> 11</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRAZIL         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.010462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  9</t>
+    <t xml:space="preserve">0.5500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDONESIA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEORGIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  12</t>
   </si>
   <si>
     <t xml:space="preserve">0.2500</t>
   </si>
   <si>
-    <t xml:space="preserve">SWEDEN         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.010171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  7</t>
+    <t xml:space="preserve">INDIA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAUDI ARABIA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISRAEL         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEXICO         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYPRUS         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALAYSIA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINGAPORE      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREECE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOUTH AFRICA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENMARK        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWITZERLAND    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSTRIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CZECH REPUBLIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   4</t>
   </si>
   <si>
     <t xml:space="preserve">0.2000</t>
   </si>
   <si>
-    <t xml:space="preserve">GERMANY        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.009881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW ZEALAND    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.009590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  14</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOREA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  16</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRELAND        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORWAY         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BELGIUM        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  12</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRAN           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDONESIA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRANCE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEORGIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAUDI ARABIA   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISRAEL         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEXICO         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYPRUS         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALAYSIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOUTH AFRICA   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GREECE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SINGAPORE      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWITZERLAND    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DENMARK        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUSTRIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0000</t>
+    <t xml:space="preserve">POLAND         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOMBIA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINLAND        </t>
   </si>
   <si>
     <t xml:space="preserve">PORTUGAL       </t>
   </si>
   <si>
-    <t xml:space="preserve">0.1667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLOMBIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZECH REPUBLIC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINLAND        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLAND         </t>
-  </si>
-  <si>
     <t xml:space="preserve">ROMANIA        </t>
   </si>
   <si>
+    <t xml:space="preserve">LITHUANIA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAILAND       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">U ARAB EMIRATES</t>
+  </si>
+  <si>
     <t xml:space="preserve">ESTONIA        </t>
   </si>
   <si>
-    <t xml:space="preserve">0.000872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LITHUANIA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">THAILAND       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">U ARAB EMIRATES</t>
+    <t xml:space="preserve">0.000599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1</t>
   </si>
   <si>
     <t xml:space="preserve">ICELAND        </t>
   </si>
   <si>
-    <t xml:space="preserve">0.000581</t>
-  </si>
-  <si>
     <t xml:space="preserve">  0</t>
   </si>
   <si>
@@ -566,52 +560,37 @@
     <t xml:space="preserve">QATAR          </t>
   </si>
   <si>
-    <t xml:space="preserve">   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5000</t>
-  </si>
-  <si>
     <t xml:space="preserve">TANZANIA       </t>
   </si>
   <si>
+    <t xml:space="preserve">ECUADOR        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGYPT          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAZAKHSTAN     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALTA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOROCCO        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERU           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERBIA         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRI LANKA      </t>
+  </si>
+  <si>
     <t xml:space="preserve">TUNISIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECUADOR        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGYPT          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUNGARY        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAZAKHSTAN     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALTA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOROCCO        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERU           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERBIA         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLOVAKIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRI LANKA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIETNAM        </t>
   </si>
 </sst>
 </file>
@@ -1094,450 +1073,450 @@
         <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
         <v>98</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>99</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>100</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" t="s">
         <v>101</v>
-      </c>
-      <c r="E19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
         <v>104</v>
       </c>
-      <c r="B20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" t="s">
-        <v>100</v>
-      </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F20" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
         <v>119</v>
       </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>120</v>
       </c>
-      <c r="D25" t="s">
-        <v>101</v>
-      </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="F26" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F27" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" t="s">
         <v>140</v>
       </c>
-      <c r="D30" t="s">
-        <v>135</v>
-      </c>
       <c r="E30" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
@@ -1554,15 +1533,15 @@
         <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B32" t="s">
         <v>142</v>
@@ -1571,33 +1550,33 @@
         <v>143</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="F32" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" t="s">
         <v>148</v>
       </c>
-      <c r="B33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>149</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" t="s">
         <v>150</v>
-      </c>
-      <c r="E33" t="s">
-        <v>128</v>
-      </c>
-      <c r="F33" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="34">
@@ -1605,579 +1584,519 @@
         <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C34" t="s">
         <v>152</v>
       </c>
       <c r="D34" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s">
         <v>153</v>
-      </c>
-      <c r="E34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F34" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" t="s">
         <v>155</v>
       </c>
-      <c r="B35" t="s">
-        <v>150</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>156</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" t="s">
         <v>157</v>
-      </c>
-      <c r="E35" t="s">
-        <v>158</v>
-      </c>
-      <c r="F35" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" t="s">
         <v>160</v>
-      </c>
-      <c r="B36" t="s">
-        <v>150</v>
-      </c>
-      <c r="C36" t="s">
-        <v>156</v>
-      </c>
-      <c r="D36" t="s">
-        <v>146</v>
-      </c>
-      <c r="E36" t="s">
-        <v>117</v>
-      </c>
-      <c r="F36" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D37" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E37" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F37" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B38" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C38" t="s">
         <v>163</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E38" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="F38" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B39" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C39" t="s">
         <v>163</v>
       </c>
       <c r="D39" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E39" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F39" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C40" t="s">
         <v>163</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="E40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F40" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C41" t="s">
         <v>163</v>
       </c>
       <c r="D41" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="E41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F41" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>169</v>
+      </c>
+      <c r="B42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" t="s">
         <v>170</v>
       </c>
-      <c r="B42" t="s">
-        <v>153</v>
-      </c>
-      <c r="C42" t="s">
-        <v>171</v>
-      </c>
       <c r="D42" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F42" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B43" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F43" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B44" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D44" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F44" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B45" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C45" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D45" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E45" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F45" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46" t="s">
+        <v>174</v>
+      </c>
+      <c r="D46" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" t="s">
         <v>177</v>
       </c>
-      <c r="B46" t="s">
-        <v>172</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="F46" t="s">
         <v>178</v>
-      </c>
-      <c r="D46" t="s">
-        <v>172</v>
-      </c>
-      <c r="E46" t="s">
-        <v>179</v>
-      </c>
-      <c r="F46" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B47" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C47" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" t="s">
+        <v>164</v>
+      </c>
+      <c r="E47" t="s">
+        <v>177</v>
+      </c>
+      <c r="F47" t="s">
         <v>178</v>
-      </c>
-      <c r="D47" t="s">
-        <v>172</v>
-      </c>
-      <c r="E47" t="s">
-        <v>179</v>
-      </c>
-      <c r="F47" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" t="s">
+        <v>164</v>
+      </c>
+      <c r="E48" t="s">
+        <v>177</v>
+      </c>
+      <c r="F48" t="s">
         <v>178</v>
-      </c>
-      <c r="D48" t="s">
-        <v>172</v>
-      </c>
-      <c r="E48" t="s">
-        <v>179</v>
-      </c>
-      <c r="F48" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C49" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D49" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E49" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F49" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C50" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D50" t="s">
+        <v>156</v>
+      </c>
+      <c r="E50" t="s">
+        <v>130</v>
+      </c>
+      <c r="F50" t="s">
         <v>157</v>
-      </c>
-      <c r="E50" t="s">
-        <v>128</v>
-      </c>
-      <c r="F50" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C51" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" t="s">
+        <v>175</v>
+      </c>
+      <c r="E51" t="s">
+        <v>177</v>
+      </c>
+      <c r="F51" t="s">
         <v>178</v>
-      </c>
-      <c r="D51" t="s">
-        <v>157</v>
-      </c>
-      <c r="E51" t="s">
-        <v>128</v>
-      </c>
-      <c r="F51" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B52" t="s">
+        <v>175</v>
+      </c>
+      <c r="C52" t="s">
         <v>184</v>
       </c>
-      <c r="C52" t="s">
-        <v>189</v>
-      </c>
       <c r="D52" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="E52" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="F52" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" t="s">
         <v>184</v>
       </c>
-      <c r="C53" t="s">
-        <v>189</v>
-      </c>
       <c r="D53" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E53" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="F53" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B54" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" t="s">
         <v>184</v>
       </c>
-      <c r="C54" t="s">
-        <v>189</v>
-      </c>
       <c r="D54" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="E54" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="F54" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B55" t="s">
+        <v>175</v>
+      </c>
+      <c r="C55" t="s">
         <v>184</v>
       </c>
-      <c r="C55" t="s">
-        <v>189</v>
-      </c>
       <c r="D55" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E55" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F55" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B56" t="s">
+        <v>175</v>
+      </c>
+      <c r="C56" t="s">
         <v>184</v>
       </c>
-      <c r="C56" t="s">
-        <v>189</v>
-      </c>
       <c r="D56" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E56" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="F56" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B57" t="s">
+        <v>175</v>
+      </c>
+      <c r="C57" t="s">
         <v>184</v>
       </c>
-      <c r="C57" t="s">
-        <v>189</v>
-      </c>
       <c r="D57" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E57" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F57" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B58" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" t="s">
         <v>184</v>
       </c>
-      <c r="C58" t="s">
-        <v>189</v>
-      </c>
       <c r="D58" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="E58" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="F58" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B59" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59" t="s">
         <v>184</v>
       </c>
-      <c r="C59" t="s">
-        <v>189</v>
-      </c>
       <c r="D59" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="E59" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="F59" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>197</v>
-      </c>
-      <c r="B60" t="s">
-        <v>184</v>
-      </c>
-      <c r="C60" t="s">
-        <v>189</v>
-      </c>
-      <c r="D60" t="s">
         <v>157</v>
-      </c>
-      <c r="E60" t="s">
-        <v>117</v>
-      </c>
-      <c r="F60" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>198</v>
-      </c>
-      <c r="B61" t="s">
-        <v>184</v>
-      </c>
-      <c r="C61" t="s">
-        <v>189</v>
-      </c>
-      <c r="D61" t="s">
-        <v>157</v>
-      </c>
-      <c r="E61" t="s">
-        <v>117</v>
-      </c>
-      <c r="F61" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>199</v>
-      </c>
-      <c r="B62" t="s">
-        <v>184</v>
-      </c>
-      <c r="C62" t="s">
-        <v>189</v>
-      </c>
-      <c r="D62" t="s">
-        <v>157</v>
-      </c>
-      <c r="E62" t="s">
-        <v>117</v>
-      </c>
-      <c r="F62" t="s">
-        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/files/MostProdCountries.xlsx
+++ b/files/MostProdCountries.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -35,19 +35,19 @@
     <t xml:space="preserve">USA            </t>
   </si>
   <si>
-    <t xml:space="preserve">2089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1976</t>
+    <t xml:space="preserve">2082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1969</t>
   </si>
   <si>
     <t xml:space="preserve">113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0541</t>
+    <t xml:space="preserve">0.0543</t>
   </si>
   <si>
     <t xml:space="preserve">CANADA         </t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve"> 130</t>
   </si>
   <si>
-    <t xml:space="preserve">0.038945</t>
+    <t xml:space="preserve">0.039346</t>
   </si>
   <si>
     <t xml:space="preserve"> 109</t>
@@ -71,55 +71,55 @@
     <t xml:space="preserve">CHINA          </t>
   </si>
   <si>
-    <t xml:space="preserve"> 123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.036848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  96</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2195</t>
+    <t xml:space="preserve"> 116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.035109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  92</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2069</t>
   </si>
   <si>
     <t xml:space="preserve">AUSTRALIA      </t>
   </si>
   <si>
-    <t xml:space="preserve"> 112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.033553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  82</t>
+    <t xml:space="preserve"> 110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.033293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  80</t>
   </si>
   <si>
     <t xml:space="preserve"> 30</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2679</t>
+    <t xml:space="preserve">0.2727</t>
   </si>
   <si>
     <t xml:space="preserve">UNITED KINGDOM </t>
   </si>
   <si>
-    <t xml:space="preserve"> 105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.031456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  76</t>
+    <t xml:space="preserve"> 104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.031477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  75</t>
   </si>
   <si>
     <t xml:space="preserve"> 29</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2762</t>
+    <t xml:space="preserve">0.2788</t>
   </si>
   <si>
     <t xml:space="preserve">ITALY          </t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">  79</t>
   </si>
   <si>
-    <t xml:space="preserve">0.023667</t>
+    <t xml:space="preserve">0.023910</t>
   </si>
   <si>
     <t xml:space="preserve">  44</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">  68</t>
   </si>
   <si>
-    <t xml:space="preserve">0.020371</t>
+    <t xml:space="preserve">0.020581</t>
   </si>
   <si>
     <t xml:space="preserve">  63</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">SPAIN          </t>
   </si>
   <si>
-    <t xml:space="preserve">0.018874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  39</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3810</t>
+    <t xml:space="preserve">  62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3871</t>
   </si>
   <si>
     <t xml:space="preserve">JAPAN          </t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">  52</t>
   </si>
   <si>
-    <t xml:space="preserve">0.015578</t>
+    <t xml:space="preserve">0.015738</t>
   </si>
   <si>
     <t xml:space="preserve">  8</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">  51</t>
   </si>
   <si>
-    <t xml:space="preserve">0.015279</t>
+    <t xml:space="preserve">0.015436</t>
   </si>
   <si>
     <t xml:space="preserve">  41</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">  34</t>
   </si>
   <si>
-    <t xml:space="preserve">0.010186</t>
+    <t xml:space="preserve">0.010291</t>
   </si>
   <si>
     <t xml:space="preserve">  27</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">  33</t>
   </si>
   <si>
-    <t xml:space="preserve">0.009886</t>
+    <t xml:space="preserve">0.009988</t>
   </si>
   <si>
     <t xml:space="preserve">  13</t>
@@ -242,277 +242,289 @@
     <t xml:space="preserve">0.6061</t>
   </si>
   <si>
+    <t xml:space="preserve">BRAZIL         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2963</t>
+  </si>
+  <si>
     <t xml:space="preserve">GERMANY        </t>
   </si>
   <si>
-    <t xml:space="preserve">  29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  25</t>
+    <t xml:space="preserve">  23</t>
   </si>
   <si>
     <t xml:space="preserve">  4</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRAZIL         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008388</t>
+    <t xml:space="preserve">0.1481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOREA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.007869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRELAND        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRAN           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELGIUM        </t>
   </si>
   <si>
     <t xml:space="preserve">  20</t>
   </si>
   <si>
+    <t xml:space="preserve">0.006053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORWAY         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEORGIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDONESIA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAUDI ARABIA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISRAEL         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004237</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.2857</t>
   </si>
   <si>
-    <t xml:space="preserve">KOREA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  15</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 12</t>
+    <t xml:space="preserve">MEXICO         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYPRUS         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINGAPORE      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   5</t>
   </si>
   <si>
     <t xml:space="preserve">0.4444</t>
   </si>
   <si>
-    <t xml:space="preserve">IRELAND        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BELGIUM        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRAN           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORWAY         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   9</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDONESIA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEORGIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRANCE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAUDI ARABIA   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISRAEL         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEXICO         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYPRUS         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0833</t>
+    <t xml:space="preserve">GREECE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1250</t>
   </si>
   <si>
     <t xml:space="preserve">MALAYSIA       </t>
   </si>
   <si>
-    <t xml:space="preserve">0.002696</t>
+    <t xml:space="preserve">0.3750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOUTH AFRICA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWITZERLAND    </t>
   </si>
   <si>
     <t xml:space="preserve">   6</t>
   </si>
   <si>
-    <t xml:space="preserve">  3</t>
+    <t xml:space="preserve">0.001816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSTRIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CZECH REPUBLIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENMARK        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLAND         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOMBIA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINLAND        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000908</t>
   </si>
   <si>
     <t xml:space="preserve">0.3333</t>
   </si>
   <si>
-    <t xml:space="preserve">SINGAPORE      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GREECE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOUTH AFRICA   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DENMARK        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWITZERLAND    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUSTRIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZECH REPUBLIC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLAND         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLOMBIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINLAND        </t>
+    <t xml:space="preserve">LITHUANIA      </t>
   </si>
   <si>
     <t xml:space="preserve">PORTUGAL       </t>
@@ -521,73 +533,64 @@
     <t xml:space="preserve">ROMANIA        </t>
   </si>
   <si>
-    <t xml:space="preserve">LITHUANIA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000899</t>
+    <t xml:space="preserve">U ARAB EMIRATES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTONIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICELAND        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KUWAIT         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAKISTAN       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QATAR          </t>
   </si>
   <si>
     <t xml:space="preserve">THAILAND       </t>
   </si>
   <si>
-    <t xml:space="preserve">U ARAB EMIRATES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTONIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICELAND        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KUWAIT         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAKISTAN       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">QATAR          </t>
+    <t xml:space="preserve">ECUADOR        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGYPT          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAZAKHSTAN     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALTA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOROCCO        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERU           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERBIA         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRI LANKA      </t>
   </si>
   <si>
     <t xml:space="preserve">TANZANIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECUADOR        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGYPT          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAZAKHSTAN     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALTA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOROCCO        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERU           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERBIA         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRI LANKA      </t>
   </si>
   <si>
     <t xml:space="preserve">TUNISIA        </t>
@@ -1084,16 +1087,16 @@
         <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
         <v>52</v>
@@ -1184,130 +1187,130 @@
         <v>76</v>
       </c>
       <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
         <v>77</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>78</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" t="s">
         <v>79</v>
-      </c>
-      <c r="E14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" t="s">
         <v>82</v>
       </c>
-      <c r="B15" t="s">
+      <c r="F15" t="s">
         <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
         <v>87</v>
       </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>88</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>89</v>
-      </c>
-      <c r="E16" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
         <v>92</v>
-      </c>
-      <c r="B17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" t="s">
-        <v>95</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" t="s">
         <v>97</v>
-      </c>
-      <c r="B18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>100</v>
       </c>
       <c r="E18" t="s">
         <v>62</v>
       </c>
       <c r="F18" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" t="s">
         <v>102</v>
-      </c>
-      <c r="B19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
         <v>105</v>
@@ -1330,10 +1333,10 @@
         <v>110</v>
       </c>
       <c r="D21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" t="s">
         <v>111</v>
-      </c>
-      <c r="E21" t="s">
-        <v>80</v>
       </c>
       <c r="F21" t="s">
         <v>112</v>
@@ -1344,116 +1347,116 @@
         <v>113</v>
       </c>
       <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" t="s">
         <v>114</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F22" t="s">
         <v>115</v>
-      </c>
-      <c r="D22" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" t="s">
-        <v>116</v>
-      </c>
-      <c r="F22" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" t="s">
         <v>118</v>
-      </c>
-      <c r="B23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="F24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" t="s">
         <v>124</v>
       </c>
-      <c r="B25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s">
-        <v>119</v>
-      </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
         <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F27" t="s">
         <v>57</v>
@@ -1461,39 +1464,39 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B28" t="s">
         <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E28" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
         <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="F29" t="s">
         <v>138</v>
@@ -1504,36 +1507,36 @@
         <v>139</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" t="s">
         <v>141</v>
       </c>
-      <c r="B31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" t="s">
-        <v>143</v>
-      </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
         <v>145</v>
@@ -1547,136 +1550,136 @@
         <v>142</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B33" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E33" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="F33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="F34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E35" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="F35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B36" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E36" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="F36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D37" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F37" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B38" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C38" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D38" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F38" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39">
@@ -1684,153 +1687,153 @@
         <v>166</v>
       </c>
       <c r="B39" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C39" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D39" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E39" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="F39" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" t="s">
         <v>167</v>
       </c>
-      <c r="B40" t="s">
-        <v>159</v>
-      </c>
       <c r="C40" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D40" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="E40" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F40" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>171</v>
+      </c>
+      <c r="B41" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" t="s">
         <v>168</v>
       </c>
-      <c r="B41" t="s">
-        <v>159</v>
-      </c>
-      <c r="C41" t="s">
-        <v>163</v>
-      </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="E41" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F41" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" t="s">
+        <v>167</v>
+      </c>
+      <c r="C42" t="s">
+        <v>168</v>
+      </c>
+      <c r="D42" t="s">
+        <v>165</v>
+      </c>
+      <c r="E42" t="s">
+        <v>111</v>
+      </c>
+      <c r="F42" t="s">
         <v>169</v>
-      </c>
-      <c r="B42" t="s">
-        <v>149</v>
-      </c>
-      <c r="C42" t="s">
-        <v>170</v>
-      </c>
-      <c r="D42" t="s">
-        <v>164</v>
-      </c>
-      <c r="E42" t="s">
-        <v>116</v>
-      </c>
-      <c r="F42" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B43" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="C43" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D43" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E43" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F43" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B44" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C44" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D44" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E44" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F44" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C45" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D45" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E45" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="F45" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E46" t="s">
         <v>177</v>
@@ -1841,16 +1844,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C47" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E47" t="s">
         <v>177</v>
@@ -1861,156 +1864,156 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C48" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D48" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E48" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="F48" t="s">
-        <v>178</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D49" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="E49" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F49" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C50" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D50" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E50" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="F50" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B51" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C51" t="s">
         <v>184</v>
       </c>
       <c r="D51" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="E51" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="F51" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B52" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C52" t="s">
         <v>184</v>
       </c>
       <c r="D52" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E52" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="F52" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
         <v>184</v>
       </c>
       <c r="D53" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="E53" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="F53" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s">
         <v>184</v>
       </c>
       <c r="D54" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E54" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="F54" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
         <v>184</v>
       </c>
       <c r="D55" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="E55" t="s">
         <v>177</v>
@@ -2021,16 +2024,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B56" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C56" t="s">
         <v>184</v>
       </c>
       <c r="D56" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="E56" t="s">
         <v>177</v>
@@ -2041,62 +2044,62 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B57" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C57" t="s">
         <v>184</v>
       </c>
       <c r="D57" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="E57" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="F57" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C58" t="s">
         <v>184</v>
       </c>
       <c r="D58" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E58" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F58" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C59" t="s">
         <v>184</v>
       </c>
       <c r="D59" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E59" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F59" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/files/MostProdCountries.xlsx
+++ b/files/MostProdCountries.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -35,19 +35,19 @@
     <t xml:space="preserve">USA            </t>
   </si>
   <si>
-    <t xml:space="preserve">2082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0543</t>
+    <t xml:space="preserve">2105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.00475</t>
   </si>
   <si>
     <t xml:space="preserve">CANADA         </t>
@@ -56,34 +56,34 @@
     <t xml:space="preserve"> 130</t>
   </si>
   <si>
-    <t xml:space="preserve">0.039346</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 109</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1615</t>
+    <t xml:space="preserve">0.038644</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 129</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.00769</t>
   </si>
   <si>
     <t xml:space="preserve">CHINA          </t>
   </si>
   <si>
-    <t xml:space="preserve"> 116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.035109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  92</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2069</t>
+    <t xml:space="preserve"> 117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.034780</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01709</t>
   </si>
   <si>
     <t xml:space="preserve">AUSTRALIA      </t>
@@ -92,70 +92,55 @@
     <t xml:space="preserve"> 110</t>
   </si>
   <si>
-    <t xml:space="preserve">0.033293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  80</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2727</t>
+    <t xml:space="preserve">0.032699</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.00000</t>
   </si>
   <si>
     <t xml:space="preserve">UNITED KINGDOM </t>
   </si>
   <si>
-    <t xml:space="preserve"> 104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.031477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  75</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2788</t>
+    <t xml:space="preserve"> 105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.031213</t>
   </si>
   <si>
     <t xml:space="preserve">ITALY          </t>
   </si>
   <si>
-    <t xml:space="preserve">  79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.023910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  44</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4430</t>
+    <t xml:space="preserve">  81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.024078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.02469</t>
   </si>
   <si>
     <t xml:space="preserve">TURKEY         </t>
   </si>
   <si>
+    <t xml:space="preserve">  67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.019917</t>
+  </si>
+  <si>
     <t xml:space="preserve">  68</t>
   </si>
   <si>
-    <t xml:space="preserve">0.020581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0735</t>
+    <t xml:space="preserve">-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01493</t>
   </si>
   <si>
     <t xml:space="preserve">SPAIN          </t>
@@ -164,13 +149,22 @@
     <t xml:space="preserve">  62</t>
   </si>
   <si>
-    <t xml:space="preserve">0.018765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3871</t>
+    <t xml:space="preserve">0.018430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NETHERLANDS    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.016647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01786</t>
   </si>
   <si>
     <t xml:space="preserve">JAPAN          </t>
@@ -179,307 +173,211 @@
     <t xml:space="preserve">  52</t>
   </si>
   <si>
-    <t xml:space="preserve">0.015738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NETHERLANDS    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.015436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  41</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1961</t>
+    <t xml:space="preserve">0.015458</t>
   </si>
   <si>
     <t xml:space="preserve">SWEDEN         </t>
   </si>
   <si>
-    <t xml:space="preserve">  34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.010291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2059</t>
+    <t xml:space="preserve">  37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010999</t>
   </si>
   <si>
     <t xml:space="preserve">NEW ZEALAND    </t>
   </si>
   <si>
+    <t xml:space="preserve">  32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009512</t>
+  </si>
+  <si>
     <t xml:space="preserve">  33</t>
   </si>
   <si>
-    <t xml:space="preserve">0.009988</t>
+    <t xml:space="preserve">-0.03125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAZIL         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERMANY        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOREA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRELAND        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.007134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRAN           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORWAY         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELGIUM        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAUDI ARABIA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDONESIA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISRAEL         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.06250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEXICO         </t>
   </si>
   <si>
     <t xml:space="preserve">  13</t>
   </si>
   <si>
-    <t xml:space="preserve"> 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRAZIL         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GERMANY        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOREA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.007869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  14</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRELAND        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRAN           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006356</t>
+    <t xml:space="preserve">0.003864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYPRUS         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEORGIA        </t>
   </si>
   <si>
     <t xml:space="preserve">  11</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BELGIUM        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006053</t>
+    <t xml:space="preserve"> 0.08333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALAYSIA       </t>
   </si>
   <si>
     <t xml:space="preserve">  10</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORWAY         </t>
+    <t xml:space="preserve">0.002973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINGAPORE      </t>
   </si>
   <si>
     <t xml:space="preserve">   9</t>
   </si>
   <si>
-    <t xml:space="preserve"> 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GEORGIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDONESIA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAUDI ARABIA   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRANCE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISRAEL         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEXICO         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYPRUS         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SINGAPORE      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002724</t>
+    <t xml:space="preserve">0.002675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOUTH AFRICA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWITZERLAND    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREECE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENMARK        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOMBIA       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSTRIA        </t>
   </si>
   <si>
     <t xml:space="preserve">   5</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GREECE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MALAYSIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOUTH AFRICA   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWITZERLAND    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUSTRIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0000</t>
+    <t xml:space="preserve">0.001486</t>
   </si>
   <si>
     <t xml:space="preserve">CZECH REPUBLIC </t>
@@ -488,90 +386,78 @@
     <t xml:space="preserve">   4</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DENMARK        </t>
+    <t xml:space="preserve"> 0.20000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLAND         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTUGAL       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINLAND        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KUWAIT         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LITHUANIA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QATAR          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROMANIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">U ARAB EMIRATES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTONIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICELAND        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAKISTAN       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAILAND       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUNISIA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECUADOR        </t>
   </si>
   <si>
     <t xml:space="preserve">   1</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLAND         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLOMBIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINLAND        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LITHUANIA      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTUGAL       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROMANIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">U ARAB EMIRATES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTONIA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICELAND        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KUWAIT         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAKISTAN       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">QATAR          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">THAILAND       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECUADOR        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000303</t>
+    <t xml:space="preserve">0.000297</t>
   </si>
   <si>
     <t xml:space="preserve">EGYPT          </t>
   </si>
   <si>
+    <t xml:space="preserve">JORDAN         </t>
+  </si>
+  <si>
     <t xml:space="preserve">KAZAKHSTAN     </t>
   </si>
   <si>
@@ -591,9 +477,6 @@
   </si>
   <si>
     <t xml:space="preserve">TANZANIA       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUNISIA        </t>
   </si>
 </sst>
 </file>
@@ -1013,1093 +896,1113 @@
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
         <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
         <v>42</v>
-      </c>
-      <c r="B8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F25" t="s">
-        <v>125</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
         <v>97</v>
       </c>
       <c r="E27" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F30" t="s">
-        <v>143</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="E31" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="F31" t="s">
-        <v>145</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>146</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="E32" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="B33" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F33" t="s">
-        <v>151</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="F34" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E36" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F36" t="s">
-        <v>161</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="E37" t="s">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="B38" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="C38" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="E38" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="E39" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F39" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="E40" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F40" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="B41" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="D41" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="E41" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="E42" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F42" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="B43" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="D43" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="E43" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="B44" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="D44" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="E44" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="B45" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="C45" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="E45" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="F45" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="B46" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="D46" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="E46" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="F46" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="B47" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="C47" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="D47" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="E47" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="F47" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="B48" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="C48" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="D48" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="E48" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="B49" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="E49" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F49" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="B50" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="D50" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="E50" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="F50" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D51" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E51" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F51" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C52" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D52" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E52" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="F52" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="B53" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C53" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D53" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E53" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F53" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="B54" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C54" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D54" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E54" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="F54" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C55" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D55" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E55" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="F55" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C56" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="F56" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D57" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E57" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F57" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C58" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D58" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E58" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F58" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="B59" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C59" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D59" t="s">
+        <v>144</v>
+      </c>
+      <c r="E59" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
         <v>154</v>
       </c>
-      <c r="E59" t="s">
-        <v>111</v>
-      </c>
-      <c r="F59" t="s">
-        <v>155</v>
+      <c r="B60" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" t="s">
+        <v>145</v>
+      </c>
+      <c r="D60" t="s">
+        <v>144</v>
+      </c>
+      <c r="E60" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/files/MostProdCountries.xlsx
+++ b/files/MostProdCountries.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -35,94 +35,103 @@
     <t xml:space="preserve">USA            </t>
   </si>
   <si>
-    <t xml:space="preserve">2105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.00475</t>
+    <t xml:space="preserve">2145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.00606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHINA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.041367</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01389</t>
   </si>
   <si>
     <t xml:space="preserve">CANADA         </t>
   </si>
   <si>
-    <t xml:space="preserve"> 130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.038644</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 129</t>
+    <t xml:space="preserve"> 134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.038495</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 133</t>
   </si>
   <si>
     <t xml:space="preserve"> 1</t>
   </si>
   <si>
-    <t xml:space="preserve"> 0.00769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHINA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.034780</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01709</t>
+    <t xml:space="preserve"> 0.00746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNITED KINGDOM </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.031887</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.00000</t>
   </si>
   <si>
     <t xml:space="preserve">AUSTRALIA      </t>
   </si>
   <si>
-    <t xml:space="preserve"> 110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.032699</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.00000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNITED KINGDOM </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.031213</t>
+    <t xml:space="preserve"> 108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.031026</t>
   </si>
   <si>
     <t xml:space="preserve">ITALY          </t>
   </si>
   <si>
-    <t xml:space="preserve">  81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.024078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.02469</t>
+    <t xml:space="preserve">  82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.023556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.02439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPAIN          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.019535</t>
   </si>
   <si>
     <t xml:space="preserve">TURKEY         </t>
@@ -131,10 +140,7 @@
     <t xml:space="preserve">  67</t>
   </si>
   <si>
-    <t xml:space="preserve">0.019917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  68</t>
+    <t xml:space="preserve">0.019247</t>
   </si>
   <si>
     <t xml:space="preserve">-1</t>
@@ -143,46 +149,55 @@
     <t xml:space="preserve">-0.01493</t>
   </si>
   <si>
-    <t xml:space="preserve">SPAIN          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.018430</t>
-  </si>
-  <si>
     <t xml:space="preserve">NETHERLANDS    </t>
   </si>
   <si>
-    <t xml:space="preserve">  56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.016647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01786</t>
+    <t xml:space="preserve">  59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.016949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01695</t>
   </si>
   <si>
     <t xml:space="preserve">JAPAN          </t>
   </si>
   <si>
-    <t xml:space="preserve">  52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.015458</t>
+    <t xml:space="preserve">  55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015800</t>
   </si>
   <si>
     <t xml:space="preserve">SWEDEN         </t>
   </si>
   <si>
-    <t xml:space="preserve">  37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.010999</t>
+    <t xml:space="preserve">  38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAZIL         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERMANY        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009480</t>
   </si>
   <si>
     <t xml:space="preserve">NEW ZEALAND    </t>
@@ -191,34 +206,19 @@
     <t xml:space="preserve">  32</t>
   </si>
   <si>
-    <t xml:space="preserve">0.009512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  33</t>
+    <t xml:space="preserve">0.009193</t>
   </si>
   <si>
     <t xml:space="preserve">-0.03125</t>
   </si>
   <si>
-    <t xml:space="preserve">BRAZIL         </t>
+    <t xml:space="preserve">KOREA          </t>
   </si>
   <si>
     <t xml:space="preserve">  30</t>
   </si>
   <si>
-    <t xml:space="preserve">0.008918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GERMANY        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOREA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008323</t>
+    <t xml:space="preserve">0.008618</t>
   </si>
   <si>
     <t xml:space="preserve">IRELAND        </t>
@@ -227,49 +227,58 @@
     <t xml:space="preserve">  24</t>
   </si>
   <si>
-    <t xml:space="preserve">0.007134</t>
+    <t xml:space="preserve">0.006895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORWAY         </t>
   </si>
   <si>
     <t xml:space="preserve">IRAN           </t>
   </si>
   <si>
-    <t xml:space="preserve">  22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORWAY         </t>
+    <t xml:space="preserve">  23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006607</t>
   </si>
   <si>
     <t xml:space="preserve">BELGIUM        </t>
   </si>
   <si>
-    <t xml:space="preserve">  20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005945</t>
+    <t xml:space="preserve">  21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDIA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDONESIA      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005171</t>
   </si>
   <si>
     <t xml:space="preserve">SAUDI ARABIA   </t>
   </si>
   <si>
-    <t xml:space="preserve">  18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDIA          </t>
+    <t xml:space="preserve">FRANCE         </t>
   </si>
   <si>
     <t xml:space="preserve">  17</t>
   </si>
   <si>
-    <t xml:space="preserve">0.005054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDONESIA      </t>
+    <t xml:space="preserve">0.004884</t>
   </si>
   <si>
     <t xml:space="preserve">ISRAEL         </t>
@@ -278,28 +287,19 @@
     <t xml:space="preserve">  16</t>
   </si>
   <si>
-    <t xml:space="preserve">0.004756</t>
+    <t xml:space="preserve">0.004596</t>
   </si>
   <si>
     <t xml:space="preserve">-0.06250</t>
   </si>
   <si>
-    <t xml:space="preserve">FRANCE         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004162</t>
-  </si>
-  <si>
     <t xml:space="preserve">MEXICO         </t>
   </si>
   <si>
     <t xml:space="preserve">  13</t>
   </si>
   <si>
-    <t xml:space="preserve">0.003864</t>
+    <t xml:space="preserve">0.003735</t>
   </si>
   <si>
     <t xml:space="preserve">CYPRUS         </t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">  12</t>
   </si>
   <si>
-    <t xml:space="preserve">0.003567</t>
+    <t xml:space="preserve">0.003447</t>
   </si>
   <si>
     <t xml:space="preserve">GEORGIA        </t>
@@ -323,10 +323,13 @@
     <t xml:space="preserve">MALAYSIA       </t>
   </si>
   <si>
+    <t xml:space="preserve">SWITZERLAND    </t>
+  </si>
+  <si>
     <t xml:space="preserve">  10</t>
   </si>
   <si>
-    <t xml:space="preserve">0.002973</t>
+    <t xml:space="preserve">0.002873</t>
   </si>
   <si>
     <t xml:space="preserve">SINGAPORE      </t>
@@ -335,22 +338,19 @@
     <t xml:space="preserve">   9</t>
   </si>
   <si>
-    <t xml:space="preserve">0.002675</t>
+    <t xml:space="preserve">0.002585</t>
   </si>
   <si>
     <t xml:space="preserve">SOUTH AFRICA   </t>
   </si>
   <si>
-    <t xml:space="preserve">SWITZERLAND    </t>
-  </si>
-  <si>
     <t xml:space="preserve">GREECE         </t>
   </si>
   <si>
     <t xml:space="preserve">   8</t>
   </si>
   <si>
-    <t xml:space="preserve">0.002378</t>
+    <t xml:space="preserve">0.002298</t>
   </si>
   <si>
     <t xml:space="preserve">DENMARK        </t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">   7</t>
   </si>
   <si>
-    <t xml:space="preserve">0.002081</t>
+    <t xml:space="preserve">0.002011</t>
   </si>
   <si>
     <t xml:space="preserve">COLOMBIA       </t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">   6</t>
   </si>
   <si>
-    <t xml:space="preserve">0.001784</t>
+    <t xml:space="preserve">0.001724</t>
   </si>
   <si>
     <t xml:space="preserve">AUSTRIA        </t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">   5</t>
   </si>
   <si>
-    <t xml:space="preserve">0.001486</t>
+    <t xml:space="preserve">0.001436</t>
   </si>
   <si>
     <t xml:space="preserve">CZECH REPUBLIC </t>
@@ -395,19 +395,22 @@
     <t xml:space="preserve">PORTUGAL       </t>
   </si>
   <si>
-    <t xml:space="preserve">0.001189</t>
+    <t xml:space="preserve">ROMANIA        </t>
   </si>
   <si>
     <t xml:space="preserve">FINLAND        </t>
   </si>
   <si>
+    <t xml:space="preserve">0.001149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KUWAIT         </t>
+  </si>
+  <si>
     <t xml:space="preserve">   3</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KUWAIT         </t>
+    <t xml:space="preserve">0.000862</t>
   </si>
   <si>
     <t xml:space="preserve">LITHUANIA      </t>
@@ -416,7 +419,7 @@
     <t xml:space="preserve">QATAR          </t>
   </si>
   <si>
-    <t xml:space="preserve">ROMANIA        </t>
+    <t xml:space="preserve">THAILAND       </t>
   </si>
   <si>
     <t xml:space="preserve">U ARAB EMIRATES</t>
@@ -428,7 +431,7 @@
     <t xml:space="preserve">   2</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000595</t>
+    <t xml:space="preserve">0.000575</t>
   </si>
   <si>
     <t xml:space="preserve">ICELAND        </t>
@@ -437,9 +440,6 @@
     <t xml:space="preserve">PAKISTAN       </t>
   </si>
   <si>
-    <t xml:space="preserve">THAILAND       </t>
-  </si>
-  <si>
     <t xml:space="preserve">TUNISIA        </t>
   </si>
   <si>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">   1</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000297</t>
+    <t xml:space="preserve">0.000287</t>
   </si>
   <si>
     <t xml:space="preserve">EGYPT          </t>
@@ -471,6 +471,9 @@
   </si>
   <si>
     <t xml:space="preserve">SERBIA         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLOVAKIA       </t>
   </si>
   <si>
     <t xml:space="preserve">SRI LANKA      </t>
@@ -939,7 +942,7 @@
         <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
         <v>36</v>
@@ -956,67 +959,67 @@
         <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
         <v>43</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
         <v>44</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
         <v>46</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
         <v>49</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
         <v>51</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>52</v>
       </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
         <v>27</v>
@@ -1027,16 +1030,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
         <v>54</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>55</v>
       </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -1047,36 +1050,36 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" t="s">
         <v>57</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>58</v>
       </c>
-      <c r="C13" t="s">
-        <v>59</v>
-      </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -1087,7 +1090,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
         <v>63</v>
@@ -1096,13 +1099,13 @@
         <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1150,13 +1153,13 @@
         <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -1167,16 +1170,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
         <v>75</v>
       </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -1276,33 +1279,33 @@
         <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
         <v>90</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>91</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" t="s">
         <v>92</v>
-      </c>
-      <c r="D25" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="26">
@@ -1359,7 +1362,7 @@
         <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F28" t="s">
         <v>101</v>
@@ -1370,13 +1373,13 @@
         <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -1387,16 +1390,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" t="s">
         <v>105</v>
       </c>
-      <c r="B30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
       <c r="D30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -1407,16 +1410,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" t="s">
         <v>108</v>
       </c>
-      <c r="B31" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>106</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -1430,13 +1433,13 @@
         <v>109</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" t="s">
         <v>107</v>
-      </c>
-      <c r="D32" t="s">
-        <v>106</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -1539,7 +1542,7 @@
         <v>123</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F37" t="s">
         <v>124</v>
@@ -1570,13 +1573,13 @@
         <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -1587,16 +1590,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -1607,16 +1610,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B41" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" t="s">
         <v>129</v>
       </c>
-      <c r="C41" t="s">
-        <v>130</v>
-      </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -1627,16 +1630,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>130</v>
+      </c>
+      <c r="B42" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" t="s">
         <v>132</v>
       </c>
-      <c r="B42" t="s">
-        <v>129</v>
-      </c>
-      <c r="C42" t="s">
-        <v>130</v>
-      </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
@@ -1650,13 +1653,13 @@
         <v>133</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -1670,13 +1673,13 @@
         <v>134</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D44" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -1690,13 +1693,13 @@
         <v>135</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C45" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D45" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -1710,13 +1713,13 @@
         <v>136</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -1727,16 +1730,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" t="s">
         <v>139</v>
       </c>
-      <c r="B47" t="s">
-        <v>137</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>138</v>
-      </c>
-      <c r="D47" t="s">
-        <v>137</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -1750,13 +1753,13 @@
         <v>140</v>
       </c>
       <c r="B48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48" t="s">
         <v>138</v>
-      </c>
-      <c r="D48" t="s">
-        <v>137</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -1770,13 +1773,13 @@
         <v>141</v>
       </c>
       <c r="B49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C49" t="s">
+        <v>139</v>
+      </c>
+      <c r="D49" t="s">
         <v>138</v>
-      </c>
-      <c r="D49" t="s">
-        <v>137</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -1790,13 +1793,13 @@
         <v>142</v>
       </c>
       <c r="B50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" t="s">
         <v>138</v>
-      </c>
-      <c r="D50" t="s">
-        <v>137</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2002,6 +2005,26 @@
         <v>27</v>
       </c>
       <c r="F60" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>155</v>
+      </c>
+      <c r="B61" t="s">
+        <v>144</v>
+      </c>
+      <c r="C61" t="s">
+        <v>145</v>
+      </c>
+      <c r="D61" t="s">
+        <v>144</v>
+      </c>
+      <c r="E61" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" t="s">
         <v>28</v>
       </c>
     </row>
